--- a/credit_application_forms/018_home_modernization_credit_application_form--credit_application_forms.xlsx
+++ b/credit_application_forms/018_home_modernization_credit_application_form--credit_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>project_type_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Type 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1136,529 +1136,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>contract_date</t>
+          <t>home_value_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Contract Date</t>
+          <t>Home Value 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>credit_status</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Credit Status</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>loan_type</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Loan Type</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>loan_term</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Loan Term</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>credit_amount</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Credit Amount</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>interest_rate</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Interest Rate</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>loan_interest</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Loan Interest</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>loan_fee</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Loan Fee</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>credit_term</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Credit Term</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>payment_term</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Payment Term</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>loan_status</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Loan Status</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>additional_info_1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Additional Info 1</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>additional_info_2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Additional Info 2</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>additional_info_3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Additional Info 3</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>additional_info_4</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Additional Info 4</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>additional_info_5</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Additional Info 5</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>additional_info_6</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Additional Info 6</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>additional_info_7</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Additional Info 7</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>additional_info_8</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Additional Info 8</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>additional_info_9</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Additional Info 9</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>additional_info_10</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Additional Info 10</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1167,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1706,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'home_renovation'}</t>
+          <t>home_renovation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Home Renovation'}</t>
+          <t>Home Renovation</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'home_addition'}</t>
+          <t>home_addition</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Home Addition'}</t>
+          <t>Home Addition</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'home_extension'}</t>
+          <t>home_extension</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Home Extension'}</t>
+          <t>Home Extension</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'6_months'}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '6 months'}</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'12_months'}</t>
+          <t>12_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '12 months'}</t>
+          <t>12 months</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'24_months'}</t>
+          <t>24_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '24 months'}</t>
+          <t>24 months</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'6%',_'id':_10}</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '6%', 'id': 10}</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'8%',_'id':_11}</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '8%', 'id': 11}</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'10%'}</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '10%'}</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'12%',_'id':_12}</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '12%', 'id': 12}</t>
+          <t>12%</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'14%',_'id':_13}</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '14%', 'id': 13}</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_'16%',_'id':_14}</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': '16%', 'id': 14}</t>
+          <t>16%</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_7,_'label':_'18%',_'id':_15}</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 7, 'label': '18%', 'id': 15}</t>
+          <t>18%</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_8,_'label':_'20%',_'id':_16}</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 8, 'label': '20%', 'id': 16}</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_9,_'label':_'22%',_'id':_17}</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 9, 'label': '22%', 'id': 17}</t>
+          <t>22%</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_10,_'label':_'24%',_'id':_18}</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 10, 'label': '24%', 'id': 18}</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_11,_'label':_'26%',_'id':_19}</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 11, 'label': '26%', 'id': 19}</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_12,_'label':_'28%',_'id':_20}</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 12, 'label': '28%', 'id': 20}</t>
+          <t>28%</t>
         </is>
       </c>
     </row>
@@ -2012,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_13,_'label':_'30%',_'id':_21}</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 13, 'label': '30%', 'id': 21}</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -2029,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_14,_'label':_'32%',_'id':_22}</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 14, 'label': '32%', 'id': 22}</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
@@ -2046,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_15,_'label':_'34%',_'id':_23}</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 15, 'label': '34%', 'id': 23}</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -2063,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_16,_'label':_'36%',_'id':_24}</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 16, 'label': '36%', 'id': 24}</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -2080,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_17,_'label':_'38%',_'id':_25}</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 17, 'label': '38%', 'id': 25}</t>
+          <t>38%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +1591,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_18,_'label':_'40%',_'id':_26}</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 18, 'label': '40%', 'id': 26}</t>
+          <t>40%</t>
         </is>
       </c>
     </row>
@@ -2114,12 +1608,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_19,_'label':_'42%',_'id':_27}</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 19, 'label': '42%', 'id': 27}</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -2131,12 +1625,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_20,_'label':_'44%',_'id':_28}</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 20, 'label': '44%', 'id': 28}</t>
+          <t>44%</t>
         </is>
       </c>
     </row>
@@ -2148,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_21,_'label':_'46%',_'id':_29}</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 21, 'label': '46%', 'id': 29}</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -2165,12 +1659,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_22,_'label':_'48%',_'id':_30}</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 22, 'label': '48%', 'id': 30}</t>
+          <t>48%</t>
         </is>
       </c>
     </row>
@@ -2182,12 +1676,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_23,_'label':_'50%',_'id':_31}</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 23, 'label': '50%', 'id': 31}</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -2199,12 +1693,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_24,_'label':_'52%',_'id':_32}</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 24, 'label': '52%', 'id': 32}</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +1710,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_25,_'label':_'54%',_'id':_33}</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 25, 'label': '54%', 'id': 33}</t>
+          <t>54%</t>
         </is>
       </c>
     </row>
@@ -2233,12 +1727,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_26,_'label':_'56%',_'id':_34}</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 26, 'label': '56%', 'id': 34}</t>
+          <t>56%</t>
         </is>
       </c>
     </row>
@@ -2250,12 +1744,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_27,_'label':_'58%',_'id':_35}</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 27, 'label': '58%', 'id': 35}</t>
+          <t>58%</t>
         </is>
       </c>
     </row>
@@ -2267,12 +1761,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_28,_'label':_'60%',_'id':_36}</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 28, 'label': '60%', 'id': 36}</t>
+          <t>60%</t>
         </is>
       </c>
     </row>
@@ -2284,12 +1778,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_29,_'label':_'62%',_'id':_37}</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 29, 'label': '62%', 'id': 37}</t>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -2301,12 +1795,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_30,_'label':_'64%',_'id':_38}</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 30, 'label': '64%', 'id': 38}</t>
+          <t>64%</t>
         </is>
       </c>
     </row>
@@ -2318,12 +1812,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_31,_'label':_'66%',_'id':_39}</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 31, 'label': '66%', 'id': 39}</t>
+          <t>66%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +1829,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_32,_'label':_'68%',_'id':_40}</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 32, 'label': '68%', 'id': 40}</t>
+          <t>68%</t>
         </is>
       </c>
     </row>
@@ -2352,12 +1846,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_33,_'label':_'70%',_'id':_41}</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 33, 'label': '70%', 'id': 41}</t>
+          <t>70%</t>
         </is>
       </c>
     </row>
@@ -2369,12 +1863,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_34,_'label':_'72%',_'id':_42}</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 34, 'label': '72%', 'id': 42}</t>
+          <t>72%</t>
         </is>
       </c>
     </row>
@@ -2386,12 +1880,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_35,_'label':_'74%',_'id':_43}</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 35, 'label': '74%', 'id': 43}</t>
+          <t>74%</t>
         </is>
       </c>
     </row>
@@ -2403,1015 +1897,369 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_36,_'label':_'76%',_'id':_44}</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 36, 'label': '76%', 'id': 44}</t>
+          <t>76%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_frequency_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_37,_'label':_'78%',_'id':_45}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 37, 'label': '78%', 'id': 45}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_frequency_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_38,_'label':_'80%',_'id':_46}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 38, 'label': '80%', 'id': 46}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_frequency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_39,_'label':_'82%',_'id':_47}</t>
+          <t>bi-annual</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 39, 'label': '82%', 'id': 47}</t>
+          <t>Bi-Annual</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_frequency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_40,_'label':_'84%',_'id':_48}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 40, 'label': '84%', 'id': 48}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_41,_'label':_'86%',_'id':_49}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 41, 'label': '86%', 'id': 49}</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_42,_'label':_'88%',_'id':_50}</t>
+          <t>12_months</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 42, 'label': '88%', 'id': 50}</t>
+          <t>12 months</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_43,_'label':_'90%',_'id':_51}</t>
+          <t>24_months</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 43, 'label': '90%', 'id': 51}</t>
+          <t>24 months</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_44,_'label':_'92%',_'id':_52}</t>
+          <t>36_months</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 44, 'label': '92%', 'id': 52}</t>
+          <t>36 months</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_45,_'label':_'94%',_'id':_53}</t>
+          <t>48_months</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 45, 'label': '94%', 'id': 53}</t>
+          <t>48 months</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_46,_'label':_'96%',_'id':_54}</t>
+          <t>bi-monthly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 46, 'label': '96%', 'id': 54}</t>
+          <t>Bi-Monthly</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_47,_'label':_'98%',_'id':_55}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 47, 'label': '98%', 'id': 55}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>loan_interest_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_48,_'label':_'100%',_'id':_56}</t>
+          <t>semi-monthly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 48, 'label': '100%', 'id': 56}</t>
+          <t>Semi-Monthly</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>loan_frequency_choices</t>
+          <t>payment_frequency_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'monthly'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Monthly'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>loan_frequency_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'quarterly'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Quarterly'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>loan_frequency_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'bi-annual'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Bi-Annual'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>loan_frequency_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'annually'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Annually'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'6_months'}</t>
+          <t>home_renovation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '6 months'}</t>
+          <t>Home Renovation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'12_months'}</t>
+          <t>home_addition</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '12 months'}</t>
+          <t>Home Addition</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'24_months'}</t>
+          <t>home_extension</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '24 months'}</t>
+          <t>Home Extension</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>contract_signed_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'36_months'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '36 months'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>contract_signed_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'48_months'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '48 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'bi-monthly'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Bi-Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'quarterly'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Quarterly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'semi-monthly'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Semi-Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'annually'}</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Annually'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'active'}</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Active'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'inactive'}</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Inactive'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'suspended'}</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Suspended'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>project_type_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'home_renovation'}</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Home Renovation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>project_type_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'home_addition'}</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Home Addition'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>project_type_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'home_extension'}</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Home Extension'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>contract_signed_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>contract_signed_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>contract_signed_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'undisclosed'}</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Undisclosed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>credit_status_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'approved'}</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Approved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>credit_status_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'denied'}</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Denied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>credit_status_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'under_review'}</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Under Review'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>credit_status_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'withdrawn'}</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Withdrawn'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>credit_status_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'pending'}</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': 'Pending'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>loan_type_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'unsecured'}</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Unsecured'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>loan_type_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'secured'}</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Secured'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>loan_term_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'short_term'}</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Short Term'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>loan_term_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'long_term'}</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Long Term'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>loan_term_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'medium_term'}</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Medium Term'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>credit_term_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'6_months'}</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': '6 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>credit_term_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'12_months'}</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': '12 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>credit_term_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'24_months'}</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': '24 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>credit_term_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'36_months'}</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': '36 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>credit_term_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'48_months'}</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': '48 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>payment_term_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'6_months'}</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': '6 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>payment_term_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'12_months'}</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': '12 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>payment_term_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'24_months'}</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': '24 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>payment_term_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'36_months'}</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': '36 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>payment_term_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'48_months'}</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': '48 months'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>{'value':_1,_'label':_'approved'}</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>{'value': 1, 'label': 'Approved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'denied'}</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Denied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'under_review'}</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Under Review'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>{'value':_4,_'label':_'withdrawn'}</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>{'value': 4, 'label': 'Withdrawn'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>{'value':_5,_'label':_'pending'}</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>{'value': 5, 'label': 'Pending'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
